--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486698_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486698_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.8756</v>
+        <v>9.623200000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1211</v>
+        <v>5.6452</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7545</v>
+        <v>3.978</v>
       </c>
       <c r="G2" t="n">
         <v>6.1894</v>
@@ -610,13 +610,13 @@
         <v>2.51</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5334</v>
+        <v>-0.7859</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0485</v>
+        <v>-0.5244</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4849</v>
+        <v>-0.2615</v>
       </c>
       <c r="V2" t="n">
         <v>3.6404</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.0655</v>
+        <v>7.0339</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3799</v>
+        <v>3.8697</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6857</v>
+        <v>3.1642</v>
       </c>
       <c r="G3" t="n">
         <v>3.569</v>
@@ -688,13 +688,13 @@
         <v>2.51</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0871</v>
+        <v>0.0554</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2753</v>
+        <v>-0.2349</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8118</v>
+        <v>0.2903</v>
       </c>
       <c r="V3" t="n">
         <v>0.8995</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.7863</v>
+        <v>6.5131</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5627</v>
+        <v>3.1902</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2236</v>
+        <v>3.3229</v>
       </c>
       <c r="G4" t="n">
         <v>2.9406</v>
@@ -766,13 +766,13 @@
         <v>2.3169</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3127</v>
+        <v>-0.5859</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1036</v>
+        <v>-0.4762</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2091</v>
+        <v>-0.1098</v>
       </c>
       <c r="V4" t="n">
         <v>1.8415</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5927</v>
+        <v>1.2135</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9033</v>
+        <v>-1.1584</v>
       </c>
       <c r="F5" t="n">
-        <v>2.496</v>
+        <v>2.3719</v>
       </c>
       <c r="G5" t="n">
         <v>3.049</v>
@@ -844,13 +844,13 @@
         <v>1.5446</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4136</v>
+        <v>-0.7929</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0825</v>
+        <v>-0.1726</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4961</v>
+        <v>-0.6203</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6565</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SANTOLARIA MARTIN</t>
+          <t>S. GUTIERREZ ROA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3975</v>
+        <v>0.2619</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0849</v>
+        <v>-1.642</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4823</v>
+        <v>1.9039</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6598000000000001</v>
+        <v>1.5083</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0139</v>
+        <v>1.0065</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6737</v>
+        <v>0.5018</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4432</v>
+        <v>-0.2216</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5653</v>
+        <v>0.3865</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1221</v>
+        <v>-0.6081</v>
       </c>
       <c r="M6" t="n">
-        <v>1.103</v>
+        <v>1.7299</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5514</v>
+        <v>0.62</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5516</v>
+        <v>1.1099</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9654</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9654</v>
+        <v>0.7723</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.7445000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3584</v>
+        <v>-0.7174</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3584</v>
+        <v>-0.0271</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2277</v>
+        <v>0.6565</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2277</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. GUTIERREZ ROA</t>
+          <t>A. GUERRERO PAEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3115</v>
+        <v>0.0919</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.642</v>
+        <v>-0.8112</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9536</v>
+        <v>0.9032</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5083</v>
+        <v>0.0019</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0065</v>
+        <v>-0.8345</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5018</v>
+        <v>0.8364</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2216</v>
+        <v>-0.6251</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3865</v>
+        <v>-1.3169</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6081</v>
+        <v>0.6918</v>
       </c>
       <c r="M7" t="n">
-        <v>1.7299</v>
+        <v>0.6271</v>
       </c>
       <c r="N7" t="n">
-        <v>0.62</v>
+        <v>0.4824</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1099</v>
+        <v>0.1447</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1585</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7723</v>
+        <v>0.3862</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6948</v>
+        <v>-0.5585</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7174</v>
+        <v>-0.4484</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0225</v>
+        <v>-0.1101</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6565</v>
+        <v>1.2277</v>
       </c>
       <c r="W7" t="n">
         <v>1.2277</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. GUERRERO PAEZ</t>
+          <t>J. SANTOLARIA MARTIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1375</v>
+        <v>0.0872</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9146</v>
+        <v>-0.3951</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0521</v>
+        <v>0.4823</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0019</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8345</v>
+        <v>-0.0139</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8364</v>
+        <v>0.6737</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6251</v>
+        <v>-0.4432</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3169</v>
+        <v>-0.5653</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6918</v>
+        <v>0.1221</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6271</v>
+        <v>1.103</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4824</v>
+        <v>0.5514</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1447</v>
+        <v>0.5516</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3862</v>
+        <v>0.9654</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5129</v>
+        <v>-0.3103</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5518</v>
+        <v>0.0481</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0389</v>
+        <v>-0.3584</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2277</v>
+        <v>-1.2277</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6855</v>
+        <v>-0.7311</v>
       </c>
       <c r="E10" t="n">
-        <v>0.133</v>
+        <v>0.2364</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8185</v>
+        <v>-0.9675</v>
       </c>
       <c r="G10" t="n">
         <v>2.1298</v>
@@ -1234,13 +1234,13 @@
         <v>0.1931</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5956</v>
+        <v>-0.6412</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4966</v>
+        <v>-0.3932</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.099</v>
+        <v>-0.248</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4128</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3943</v>
+        <v>-2.3459</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7218</v>
+        <v>-4.9217</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3275</v>
+        <v>2.5759</v>
       </c>
       <c r="G11" t="n">
         <v>-0.0567</v>
@@ -1312,13 +1312,13 @@
         <v>1.3515</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4415</v>
+        <v>-0.393</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1934</v>
+        <v>-0.3933</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.248</v>
+        <v>0.0003</v>
       </c>
       <c r="V11" t="n">
         <v>0.6138</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4283</v>
+        <v>-3.7152</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1556</v>
+        <v>-3.7902</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2727</v>
+        <v>0.075</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4809</v>
@@ -1390,13 +1390,13 @@
         <v>1.3515</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1751</v>
+        <v>-0.462</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7725</v>
+        <v>-0.4071</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4025</v>
+        <v>-0.0549</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2277</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.5272</v>
+        <v>-4.3493</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2904</v>
+        <v>-2.187</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2368</v>
+        <v>-2.1623</v>
       </c>
       <c r="G13" t="n">
         <v>0.1775</v>
@@ -1468,13 +1468,13 @@
         <v>0.5792</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6122</v>
+        <v>-0.4342</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3863</v>
+        <v>-0.2829</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2259</v>
+        <v>-0.1514</v>
       </c>
       <c r="V13" t="n">
         <v>-2.741</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.9244</v>
+        <v>13.4763</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.515899999999998</v>
+        <v>-1.964099999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>15.4404</v>
+        <v>15.4406</v>
       </c>
       <c r="G14" t="n">
         <v>19.4808</v>
@@ -1534,7 +1534,7 @@
         <v>1.0275</v>
       </c>
       <c r="O14" t="n">
-        <v>9.720400000000001</v>
+        <v>9.720399999999998</v>
       </c>
       <c r="P14" t="n">
         <v>-0.9654</v>
@@ -1546,16 +1546,16 @@
         <v>14.4807</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.204700000000001</v>
+        <v>-5.652999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.553900000000001</v>
+        <v>-4.0023</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.6507</v>
+        <v>-1.6509</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6137000000000006</v>
+        <v>0.6136999999999997</v>
       </c>
       <c r="W14" t="n">
         <v>8.7515</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4918</v>
+        <v>2.8628</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0047</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4871</v>
+        <v>2.0649</v>
       </c>
       <c r="G15" t="n">
         <v>-0.7692</v>
@@ -1624,13 +1624,13 @@
         <v>2.7031</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7597</v>
+        <v>1.1307</v>
       </c>
       <c r="T15" t="n">
-        <v>0.551</v>
+        <v>0.3441</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2087</v>
+        <v>0.7866</v>
       </c>
       <c r="V15" t="n">
         <v>4.6251</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7687</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3057</v>
+        <v>1.4091</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.537</v>
+        <v>-0.5618</v>
       </c>
       <c r="G16" t="n">
         <v>-1.656</v>
@@ -1702,13 +1702,13 @@
         <v>0.5792</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6177</v>
+        <v>0.6963</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3584</v>
+        <v>0.4618</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2594</v>
+        <v>0.2345</v>
       </c>
       <c r="V16" t="n">
         <v>1.2277</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ONGIL FERNANDEZ</t>
+          <t>A. MARTÍNEZ LAGO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9584</v>
+        <v>-0.5147</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.0752</v>
+        <v>-1.9347</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1168</v>
+        <v>1.42</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.9584</v>
+        <v>-2.6758</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.0067</v>
+        <v>-0.7588</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9517</v>
+        <v>-1.917</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.6958</v>
+        <v>-2.3441</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.0064</v>
+        <v>-0.2756</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6895</v>
+        <v>-2.0684</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2626</v>
+        <v>-0.3318</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0003</v>
+        <v>-0.4832</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2623</v>
+        <v>0.1514</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5792</v>
+        <v>1.1585</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.1931</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7723</v>
+        <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1931</v>
+        <v>0.717</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4139</v>
+        <v>0.3169</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6071</v>
+        <v>0.4002</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2277</v>
+        <v>0.2856</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2277</v>
+        <v>0.2856</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MARTÍNEZ LAGO</t>
+          <t>J. ONGIL FERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2097</v>
+        <v>-0.8757</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5552</v>
+        <v>-1.8683</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3455</v>
+        <v>0.9926</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.6758</v>
+        <v>-2.9584</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7588</v>
+        <v>-2.0067</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.917</v>
+        <v>-0.9517</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.3441</v>
+        <v>-2.6958</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2756</v>
+        <v>-2.0064</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.0684</v>
+        <v>-0.6895</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3318</v>
+        <v>-0.2626</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4832</v>
+        <v>-0.0003</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1514</v>
+        <v>-0.2623</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1585</v>
+        <v>0.5792</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.1931</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3515</v>
+        <v>0.7723</v>
       </c>
       <c r="S18" t="n">
-        <v>0.022</v>
+        <v>0.2758</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3037</v>
+        <v>-0.2071</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3257</v>
+        <v>0.4829</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2856</v>
+        <v>1.2277</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2856</v>
+        <v>1.2277</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4913</v>
+        <v>-0.9616</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8893</v>
+        <v>-2.6824</v>
       </c>
       <c r="F19" t="n">
-        <v>1.398</v>
+        <v>1.7208</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6208</v>
@@ -1936,13 +1936,13 @@
         <v>0.7723</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3918</v>
+        <v>0.1379</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.607</v>
+        <v>-0.4002</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2152</v>
+        <v>0.538</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2856</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5084</v>
+        <v>-1.4339</v>
       </c>
       <c r="E20" t="n">
         <v>-3.4246</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9161</v>
+        <v>1.9906</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1451</v>
@@ -2014,13 +2014,13 @@
         <v>1.5446</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6287</v>
+        <v>0.7032</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3039</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9326</v>
+        <v>1.0071</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5712</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MARTÍNEZ BRUNO</t>
+          <t>J. VALVERDE SASTRE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5606</v>
+        <v>-1.8667</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0187</v>
+        <v>0.3546</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5419</v>
+        <v>-2.2213</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7804</v>
+        <v>-0.2899</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7857</v>
+        <v>0.1103</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9947</v>
+        <v>-0.4002</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.0273</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0265</v>
+        <v>-0.0273</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6081</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1458</v>
+        <v>-0.2626</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7591</v>
+        <v>0.1376</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3866</v>
+        <v>-0.4002</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5446</v>
+        <v>0.3862</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7377</v>
+        <v>0.3862</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1306</v>
+        <v>0.2068</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5235</v>
+        <v>0.0964</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6071</v>
+        <v>0.1105</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.4554</v>
+        <v>-2.1698</v>
       </c>
       <c r="W21" t="n">
         <v>0.2856</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.741</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. VALVERDE SASTRE</t>
+          <t>J. MARTÍNEZ BRUNO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8585</v>
+        <v>-2.0777</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5615</v>
+        <v>-0.5358000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.42</v>
+        <v>-1.5419</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2899</v>
+        <v>-1.7804</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1103</v>
+        <v>-0.7857</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4002</v>
+        <v>-0.9947</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0273</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0273</v>
+        <v>-0.0265</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-0.6081</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2626</v>
+        <v>-1.1458</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1376</v>
+        <v>-0.7591</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4002</v>
+        <v>-0.3866</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3862</v>
+        <v>1.5446</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3862</v>
+        <v>1.7377</v>
       </c>
       <c r="S22" t="n">
-        <v>0.215</v>
+        <v>0.6135</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3032</v>
+        <v>0.0063</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0882</v>
+        <v>0.6071</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.1698</v>
+        <v>-2.4554</v>
       </c>
       <c r="W22" t="n">
         <v>0.2856</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4554</v>
+        <v>-2.741</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0097</v>
+        <v>-2.1009</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5685</v>
+        <v>-2.3617</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5588</v>
+        <v>0.2608</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9972</v>
@@ -2248,13 +2248,13 @@
         <v>2.3169</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7944</v>
+        <v>0.7032</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0833</v>
+        <v>0.1235</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8777</v>
+        <v>0.5797</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2277</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0627</v>
+        <v>-3.1951</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9115</v>
+        <v>-2.1183</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1512</v>
+        <v>-1.0767</v>
       </c>
       <c r="G24" t="n">
         <v>-2.6141</v>
@@ -2326,13 +2326,13 @@
         <v>1.5446</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4356</v>
+        <v>0.3032</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.3996</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1708</v>
+        <v>-0.0963</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2703</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.5256</v>
+        <v>-3.6083</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.8694</v>
+        <v>-3.0763</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6562</v>
+        <v>-0.532</v>
       </c>
       <c r="G25" t="n">
         <v>-2.9737</v>
@@ -2404,13 +2404,13 @@
         <v>1.7377</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7997</v>
+        <v>0.717</v>
       </c>
       <c r="T25" t="n">
-        <v>1.0201</v>
+        <v>0.8133</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2204</v>
+        <v>-0.0963</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-12.9244</v>
+        <v>-12.9245</v>
       </c>
       <c r="E26" t="n">
         <v>-15.4405</v>
       </c>
       <c r="F26" t="n">
-        <v>2.515999999999999</v>
+        <v>2.516000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-19.4806</v>
@@ -2482,13 +2482,13 @@
         <v>15.4461</v>
       </c>
       <c r="S26" t="n">
-        <v>6.2047</v>
+        <v>6.204599999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>1.6508</v>
+        <v>1.6507</v>
       </c>
       <c r="U26" t="n">
-        <v>4.5541</v>
+        <v>4.553999999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-0.613899999999999</v>
